--- a/supplementary/Supplementary_Table_1_Cohorts_and_QC.xlsx
+++ b/supplementary/Supplementary_Table_1_Cohorts_and_QC.xlsx
@@ -8,42 +8,50 @@
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cohort_manifest" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Discovery_metadata" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="External_metadata" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sample_count_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="QC_GSE138266" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="QC_GSE194078" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="QC_GSE286068" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="QC_GSE328265" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Cohort_analysis_roles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Cohort_manifest" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Discovery_metadata" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="External_metadata" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sample_count_summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="QC_GSE138266" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="QC_GSE194078" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="QC_GSE286068" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="QC_GSE328265" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Postdecont_expression_QC" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$10:$F$18</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Overview'!$A$1:$F$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cohort_manifest'!$A$4:$D$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Cohort_manifest'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Cohort_manifest'!$A$1:$D$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Discovery_metadata'!$A$4:$M$74</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Discovery_metadata'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Discovery_metadata'!$A$1:$M$74</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'External_metadata'!$A$4:$J$35</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'External_metadata'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'External_metadata'!$A$1:$J$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sample_count_summary'!$A$4:$E$21</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Sample_count_summary'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Sample_count_summary'!$A$1:$E$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'QC_GSE138266'!$A$4:$I$26</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'QC_GSE138266'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'QC_GSE138266'!$A$1:$I$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'QC_GSE194078'!$A$4:$I$26</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'QC_GSE194078'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'QC_GSE194078'!$A$1:$I$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'QC_GSE286068'!$A$4:$I$19</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'QC_GSE286068'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'QC_GSE286068'!$A$1:$I$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'QC_GSE328265'!$A$4:$K$35</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'QC_GSE328265'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'QC_GSE328265'!$A$1:$K$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$10:$F$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Overview'!$A$1:$F$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cohort_analysis_roles'!$A$4:$H$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Cohort_analysis_roles'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Cohort_analysis_roles'!$A$1:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cohort_manifest'!$A$4:$D$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cohort_manifest'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cohort_manifest'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Discovery_metadata'!$A$4:$M$74</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Discovery_metadata'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Discovery_metadata'!$A$1:$M$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'External_metadata'!$A$4:$J$35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'External_metadata'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'External_metadata'!$A$1:$J$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Sample_count_summary'!$A$4:$E$21</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Sample_count_summary'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Sample_count_summary'!$A$1:$E$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'QC_GSE138266'!$A$4:$I$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'QC_GSE138266'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'QC_GSE138266'!$A$1:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'QC_GSE194078'!$A$4:$I$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'QC_GSE194078'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'QC_GSE194078'!$A$1:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'QC_GSE286068'!$A$4:$I$19</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'QC_GSE286068'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'QC_GSE286068'!$A$1:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'QC_GSE328265'!$A$4:$K$35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'QC_GSE328265'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'QC_GSE328265'!$A$1:$K$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Postdecont_expression_QC'!$A$4:$E$41</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Postdecont_expression_QC'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'Postdecont_expression_QC'!$A$1:$E$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -159,7 +167,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -197,6 +205,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -283,7 +294,38 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_Cohort_manifest" displayName="T_Cohort_manifest" ref="A4:D8" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_Cohort_analysis_roles" displayName="T_Cohort_analysis_roles" ref="A4:H8" headerRowCount="1">
+  <autoFilter ref="A4:H8"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="dataset"/>
+    <tableColumn id="2" name="paired_PBMC_CSF_root_reference"/>
+    <tableColumn id="3" name="independent_trajectory_reconstruction"/>
+    <tableColumn id="4" name="disease_discovery"/>
+    <tableColumn id="5" name="external_fixed_score_projection"/>
+    <tableColumn id="6" name="disease_comparison"/>
+    <tableColumn id="7" name="analysis_scope"/>
+    <tableColumn id="8" name="source"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="T_Postdecont_expression_QC" displayName="T_Postdecont_expression_QC" ref="A4:E41" headerRowCount="1">
+  <autoFilter ref="A4:E41"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="dataset"/>
+    <tableColumn id="2" name="sample_accession"/>
+    <tableColumn id="3" name="n_postdoublet_input"/>
+    <tableColumn id="4" name="n_postdecont_qc_pass"/>
+    <tableColumn id="5" name="n_postdecont_removed"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_Cohort_manifest" displayName="T_Cohort_manifest" ref="A4:D8" headerRowCount="1">
   <autoFilter ref="A4:D8"/>
   <tableColumns count="4">
     <tableColumn id="1" name="dataset"/>
@@ -295,8 +337,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_Discovery_metadata" displayName="T_Discovery_metadata" ref="A4:M74" headerRowCount="1">
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_Discovery_metadata" displayName="T_Discovery_metadata" ref="A4:M74" headerRowCount="1">
   <autoFilter ref="A4:M74"/>
   <tableColumns count="13">
     <tableColumn id="1" name="gse"/>
@@ -317,8 +359,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_External_metadata" displayName="T_External_metadata" ref="A4:J35" headerRowCount="1">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_External_metadata" displayName="T_External_metadata" ref="A4:J35" headerRowCount="1">
   <autoFilter ref="A4:J35"/>
   <tableColumns count="10">
     <tableColumn id="1" name="gse"/>
@@ -336,8 +378,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_Sample_count_summary" displayName="T_Sample_count_summary" ref="A4:E21" headerRowCount="1">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T_Sample_count_summary" displayName="T_Sample_count_summary" ref="A4:E21" headerRowCount="1">
   <autoFilter ref="A4:E21"/>
   <tableColumns count="5">
     <tableColumn id="1" name="gse"/>
@@ -350,26 +392,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T_QC_GSE138266" displayName="T_QC_GSE138266" ref="A4:I26" headerRowCount="1">
-  <autoFilter ref="A4:I26"/>
-  <tableColumns count="9">
-    <tableColumn id="1" name="sample_accession"/>
-    <tableColumn id="2" name="n_pre_doublet_qc"/>
-    <tableColumn id="3" name="n_scrublet_doublets"/>
-    <tableColumn id="4" name="n_scDblFinder_doublets"/>
-    <tableColumn id="5" name="n_doublet_union"/>
-    <tableColumn id="6" name="n_singlets"/>
-    <tableColumn id="7" name="pct_doublet_union"/>
-    <tableColumn id="8" name="median_decontX_contamination"/>
-    <tableColumn id="9" name="decontX_status"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="T_QC_GSE194078" displayName="T_QC_GSE194078" ref="A4:I26" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="T_QC_GSE138266" displayName="T_QC_GSE138266" ref="A4:I26" headerRowCount="1">
   <autoFilter ref="A4:I26"/>
   <tableColumns count="9">
     <tableColumn id="1" name="sample_accession"/>
@@ -387,7 +411,25 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="T_QC_GSE286068" displayName="T_QC_GSE286068" ref="A4:I19" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="T_QC_GSE194078" displayName="T_QC_GSE194078" ref="A4:I26" headerRowCount="1">
+  <autoFilter ref="A4:I26"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="sample_accession"/>
+    <tableColumn id="2" name="n_pre_doublet_qc"/>
+    <tableColumn id="3" name="n_scrublet_doublets"/>
+    <tableColumn id="4" name="n_scDblFinder_doublets"/>
+    <tableColumn id="5" name="n_doublet_union"/>
+    <tableColumn id="6" name="n_singlets"/>
+    <tableColumn id="7" name="pct_doublet_union"/>
+    <tableColumn id="8" name="median_decontX_contamination"/>
+    <tableColumn id="9" name="decontX_status"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="T_QC_GSE286068" displayName="T_QC_GSE286068" ref="A4:I19" headerRowCount="1">
   <autoFilter ref="A4:I19"/>
   <tableColumns count="9">
     <tableColumn id="1" name="sample_accession"/>
@@ -404,8 +446,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="T_QC_GSE328265" displayName="T_QC_GSE328265" ref="A4:K35" headerRowCount="1">
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="T_QC_GSE328265" displayName="T_QC_GSE328265" ref="A4:K35" headerRowCount="1">
   <autoFilter ref="A4:K35"/>
   <tableColumns count="11">
     <tableColumn id="1" name="sample_accession"/>
@@ -713,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -789,157 +831,157 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Cohort_manifest</t>
+          <t>Cohort_analysis_roles</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Dataset accessions, analysis roles and external-cohort inclusion.</t>
+          <t>Cohort eligibility for paired roots, trajectory reconstruction, disease discovery and external projection.</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>metadata/cohort_roles.csv</t>
+          <t>metadata/cohort_analysis_roles.csv</t>
         </is>
       </c>
       <c r="D11" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>257b2eb1bda7c25b9e1d7cc84682fc0b03e3b3c84109d6214e1a9c2e48039567</t>
+          <t>a8df1b1dcdc0cc6ddaf041e3d2e3a0d967b6c67ff4b61b6eb10dce3e70a98eed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Discovery_metadata</t>
+          <t>Cohort_manifest</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Harmonized discovery-cohort sample metadata.</t>
+          <t>Dataset accessions, analysis roles and external-cohort inclusion.</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>metadata/all_geo_sample_metadata.csv</t>
+          <t>metadata/cohort_roles.csv</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>c79e535632222cd2d490a71f35409d3ae9832fa4fd009df280e3f183f5593db3</t>
+          <t>257b2eb1bda7c25b9e1d7cc84682fc0b03e3b3c84109d6214e1a9c2e48039567</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>External_metadata</t>
+          <t>Discovery_metadata</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Independent external cohort sample metadata.</t>
+          <t>Sample metadata for the three trajectory cohorts; GSE194078 is excluded from disease comparisons.</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>metadata/GSE328265_sample_metadata.csv</t>
+          <t>metadata/all_geo_sample_metadata.csv</t>
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>a8b5667a53da643c7fef22cb0f7f71e8eca5b225055d2fa6870779c82277d043</t>
+          <t>0f5fa2a04ab22afad08e929d3c37432b6a9d87c66f70dc05c554f2613481dfee</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Sample_count_summary</t>
+          <t>External_metadata</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Sample and group counts used to audit metadata harmonization.</t>
+          <t>Independent external cohort sample metadata.</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>metadata/sample_count_summary.csv</t>
+          <t>metadata/GSE328265_sample_metadata.csv</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>2e2a43426d6405ae21f4195594bf922886a1a2ad5a3e28fecf0f00dceef5e4be</t>
+          <t>a8b5667a53da643c7fef22cb0f7f71e8eca5b225055d2fa6870779c82277d043</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>QC_GSE138266</t>
+          <t>Sample_count_summary</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Sample-level final QC, DecontX and doublet-union summary.</t>
+          <t>Sample and group counts used to audit metadata harmonization.</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>results/qc/GSE138266_cleanup_sample_summary.csv</t>
+          <t>metadata/sample_count_summary.csv</t>
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>7c5f4424f0a3b78273b2ac866299350c13f1fdf06bd86a4c73c9b96f6ba29012</t>
+          <t>2e2a43426d6405ae21f4195594bf922886a1a2ad5a3e28fecf0f00dceef5e4be</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>QC_GSE194078</t>
+          <t>QC_GSE138266</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Sample-level final QC, DecontX and doublet-union summary.</t>
+          <t>Sample-level doublet-union singlet counts and DecontX estimates, before post-decontamination expression filtering.</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>results/qc/GSE194078_cleanup_sample_summary.csv</t>
+          <t>results/qc/GSE138266_cleanup_sample_summary.csv</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
@@ -950,68 +992,124 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>2d8397a914a70f7c47491c513209c1dd4a5e3c65f7fca9c72050ac37e63b1008</t>
+          <t>7c5f4424f0a3b78273b2ac866299350c13f1fdf06bd86a4c73c9b96f6ba29012</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>QC_GSE286068</t>
+          <t>QC_GSE194078</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Sample-level final QC, DecontX and doublet-union summary.</t>
+          <t>Sample-level doublet-union singlet counts and DecontX estimates, before post-decontamination expression filtering.</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>results/qc/GSE286068_cleanup_sample_summary.csv</t>
+          <t>results/qc/GSE194078_cleanup_sample_summary.csv</t>
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>9</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>d11c8f190a24bf5b7f73286df60a9d4855142e88edec024ecc243d2c08482c6d</t>
+          <t>2d8397a914a70f7c47491c513209c1dd4a5e3c65f7fca9c72050ac37e63b1008</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
+          <t>QC_GSE286068</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Sample-level doublet-union singlet counts and DecontX estimates, before post-decontamination expression filtering.</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>results/qc/GSE286068_cleanup_sample_summary.csv</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>d11c8f190a24bf5b7f73286df60a9d4855142e88edec024ecc243d2c08482c6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
           <t>QC_GSE328265</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Sample-level final QC, DecontX and doublet-union summary.</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Sample-level doublet-union singlet counts and DecontX estimates, before post-decontamination expression filtering.</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>results/qc/GSE328265_cleanup_sample_summary.csv</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D19" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E19" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>319110e78b791ebae46387fc2f9b832a8134cd2ad1d9067f0f0da787677e5932</t>
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Postdecont_expression_QC</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Sample-level expression filtering after DecontX for GSE194078 and GSE286068; distinct from doublet-union singlet retention.</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>results/qc/GSE194078_postdecont_qc_summary.csv; results/qc/GSE286068_postdecont_qc_summary.csv</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>680ca7d2d35b7f410520b2ec00cb4879a5f772fc6648c92eec2c40aa3de55394; efd312e3b80a48424821de6be3bb865cc8e9f401c8d8e96e758684dc06b171ac</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A10:F18"/>
+  <autoFilter ref="A10:F20"/>
   <mergeCells count="3">
     <mergeCell ref="A7:F8"/>
     <mergeCell ref="A3:F4"/>
@@ -1026,13 +1124,2518 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Sample-level doublet-union singlet counts and DecontX estimates, before post-decontamination expression filtering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Source: results/qc/GSE328265_cleanup_sample_summary.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>sample_accession</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>subject_id</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>diagnosis</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>n_qc_pass</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>n_scrublet_doublets</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>n_scDblFinder_doublets</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>n_doublet_union</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>n_singlets</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>pct_doublet_union</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>median_decontX_contamination</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>decontX_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>GSM9651991</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Ctrl_1</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Ctrl</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>949</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>907</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <v>4.42571127502634</v>
+      </c>
+      <c r="J5" s="16" t="n">
+        <v>0.0069212043861581</v>
+      </c>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>GSM9651992</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Ctrl_3</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Ctrl</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>506</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>485</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>4.1501976284585</v>
+      </c>
+      <c r="J6" s="16" t="n">
+        <v>0.0103990633106001</v>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>GSM9651993</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Ctrl_4</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Ctrl</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>847</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>820</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>3.18772136953955</v>
+      </c>
+      <c r="J7" s="16" t="n">
+        <v>0.0065734772454175</v>
+      </c>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>GSM9651994</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Ctrl_5</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Ctrl</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>2515</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>51</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>147</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>174</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>2341</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>6.91848906560636</v>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>0.0117902681770771</v>
+      </c>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>GSM9651995</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Ctrl_6</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Ctrl</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>364</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>356</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>2.1978021978022</v>
+      </c>
+      <c r="J9" s="16" t="n">
+        <v>0.008211764616374399</v>
+      </c>
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>GSM9651996</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Ctrl_7</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Ctrl</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="I10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="16" t="n"/>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>not_run_lt_50_singlets</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>GSM9651997</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Ctrl_9</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Ctrl</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>479</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>460</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>3.96659707724426</v>
+      </c>
+      <c r="J11" s="16" t="n">
+        <v>0.101773605686458</v>
+      </c>
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>GSM9651998</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Ctrl_10</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Ctrl</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>2199</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>95</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>4.32014552069122</v>
+      </c>
+      <c r="J12" s="16" t="n">
+        <v>0.026205776626616</v>
+      </c>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>GSM9651999</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>PPMS_1</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>PPMS</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>313</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>302</v>
+      </c>
+      <c r="I13" s="16" t="n">
+        <v>3.51437699680511</v>
+      </c>
+      <c r="J13" s="16" t="n">
+        <v>0.009097831093387999</v>
+      </c>
+      <c r="K13" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>GSM9652000</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>PPMS_2</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>PPMS</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>484</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>470</v>
+      </c>
+      <c r="I14" s="16" t="n">
+        <v>2.89256198347107</v>
+      </c>
+      <c r="J14" s="16" t="n">
+        <v>0.008623103775787301</v>
+      </c>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>GSM9652001</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>PPMS_3</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>PPMS</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>244</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>235</v>
+      </c>
+      <c r="I15" s="16" t="n">
+        <v>3.68852459016393</v>
+      </c>
+      <c r="J15" s="16" t="n">
+        <v>0.0050243298464545</v>
+      </c>
+      <c r="K15" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>GSM9652002</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>PPMS_4</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>PPMS</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>243</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>232</v>
+      </c>
+      <c r="I16" s="16" t="n">
+        <v>4.52674897119342</v>
+      </c>
+      <c r="J16" s="16" t="n">
+        <v>0.0191733597514777</v>
+      </c>
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>GSM9652003</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>PPMS_5</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>PPMS</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>69</v>
+      </c>
+      <c r="I17" s="16" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="J17" s="16" t="n">
+        <v>0.0337171534663794</v>
+      </c>
+      <c r="K17" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>GSM9652004</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>RRMS_1</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>RRMS</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>527</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>505</v>
+      </c>
+      <c r="I18" s="16" t="n">
+        <v>4.17457305502846</v>
+      </c>
+      <c r="J18" s="16" t="n">
+        <v>0.008260764005817101</v>
+      </c>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>GSM9652005</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>RRMS_2</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>RRMS</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>4498</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>162</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>302</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>381</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>4117</v>
+      </c>
+      <c r="I19" s="16" t="n">
+        <v>8.47043130280125</v>
+      </c>
+      <c r="J19" s="16" t="n">
+        <v>0.0006277716992767</v>
+      </c>
+      <c r="K19" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>GSM9652006</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>RRMS_3</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>RRMS</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>10057</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>810</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>1199</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>1600</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>8457</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>15.9093168937059</v>
+      </c>
+      <c r="J20" s="16" t="n">
+        <v>0.0003035803005858</v>
+      </c>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>GSM9652007</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>RRMS_4</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>RRMS</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>1307</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>1260</v>
+      </c>
+      <c r="I21" s="16" t="n">
+        <v>3.59602142310635</v>
+      </c>
+      <c r="J21" s="16" t="n">
+        <v>0.0056808729767499</v>
+      </c>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>GSM9652008</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>RRMS_5</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>RRMS</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>400</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>385</v>
+      </c>
+      <c r="I22" s="16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J22" s="16" t="n">
+        <v>0.0114590565810807</v>
+      </c>
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>GSM9652009</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>RRMS_6</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>RRMS</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>2733</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>145</v>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>184</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>2549</v>
+      </c>
+      <c r="I23" s="16" t="n">
+        <v>6.73252835711672</v>
+      </c>
+      <c r="J23" s="16" t="n">
+        <v>0.0085876594704894</v>
+      </c>
+      <c r="K23" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>GSM9652010</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>RRMS_7</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>RRMS</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>2793</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>63</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>154</v>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>191</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>2602</v>
+      </c>
+      <c r="I24" s="16" t="n">
+        <v>6.83852488363767</v>
+      </c>
+      <c r="J24" s="16" t="n">
+        <v>0.0007245457728044</v>
+      </c>
+      <c r="K24" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>GSM9652011</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>RRMS_8</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>RRMS</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>66</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="I25" s="16" t="n">
+        <v>7.57575757575758</v>
+      </c>
+      <c r="J25" s="16" t="n">
+        <v>0.07025013731803489</v>
+      </c>
+      <c r="K25" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>GSM9652012</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>RRMS_9</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>RRMS</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>712</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>673</v>
+      </c>
+      <c r="I26" s="16" t="n">
+        <v>5.47752808988764</v>
+      </c>
+      <c r="J26" s="16" t="n">
+        <v>0.0150314566845329</v>
+      </c>
+      <c r="K26" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>GSM9652013</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>SPMS_1</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>SPMS</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>390</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="G27" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>374</v>
+      </c>
+      <c r="I27" s="16" t="n">
+        <v>4.1025641025641</v>
+      </c>
+      <c r="J27" s="16" t="n">
+        <v>0.0111916952800713</v>
+      </c>
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>GSM9652014</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>SPMS_2</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>SPMS</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>101</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>1893</v>
+      </c>
+      <c r="I28" s="16" t="n">
+        <v>5.96125186289121</v>
+      </c>
+      <c r="J28" s="16" t="n">
+        <v>0.009328309626757099</v>
+      </c>
+      <c r="K28" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>GSM9652015</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>SPMS_3</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>SPMS</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>732</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="H29" s="17" t="n">
+        <v>703</v>
+      </c>
+      <c r="I29" s="16" t="n">
+        <v>3.96174863387978</v>
+      </c>
+      <c r="J29" s="16" t="n">
+        <v>0.0132433108291693</v>
+      </c>
+      <c r="K29" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>GSM9677400</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>PPMS_6</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>PPMS</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>11808</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>1116</v>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>1296</v>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>1809</v>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>9999</v>
+      </c>
+      <c r="I30" s="16" t="n">
+        <v>15.3201219512195</v>
+      </c>
+      <c r="J30" s="16" t="n">
+        <v>0.0352331029380918</v>
+      </c>
+      <c r="K30" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>GSM9677401</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>SPMS_4</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>SPMS</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>843</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G31" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="H31" s="17" t="n">
+        <v>809</v>
+      </c>
+      <c r="I31" s="16" t="n">
+        <v>4.03321470937129</v>
+      </c>
+      <c r="J31" s="16" t="n">
+        <v>0.0002173787985738</v>
+      </c>
+      <c r="K31" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>GSM9677402</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>SPMS_4</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>SPMS</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>4371</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>153</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>264</v>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>353</v>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>4018</v>
+      </c>
+      <c r="I32" s="16" t="n">
+        <v>8.07595515900252</v>
+      </c>
+      <c r="J32" s="16" t="n">
+        <v>0.0012079561137204</v>
+      </c>
+      <c r="K32" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>GSM9677403</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>SPMS_5</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>SPMS</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="n">
+        <v>234</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="G33" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H33" s="17" t="n">
+        <v>221</v>
+      </c>
+      <c r="I33" s="16" t="n">
+        <v>5.55555555555556</v>
+      </c>
+      <c r="J33" s="16" t="n">
+        <v>0.0081235072473752</v>
+      </c>
+      <c r="K33" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>GSM9677404</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>SPMS_6</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>SPMS</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>631</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>611</v>
+      </c>
+      <c r="I34" s="16" t="n">
+        <v>3.16957210776545</v>
+      </c>
+      <c r="J34" s="16" t="n">
+        <v>0.0058398404081722</v>
+      </c>
+      <c r="K34" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>GSM9677405</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>SPMS_7</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>SPMS</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="n">
+        <v>1748</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="F35" s="17" t="n">
+        <v>79</v>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>1664</v>
+      </c>
+      <c r="I35" s="16" t="n">
+        <v>4.80549199084668</v>
+      </c>
+      <c r="J35" s="16" t="n">
+        <v>0.032806177331442</v>
+      </c>
+      <c r="K35" s="14" t="inlineStr">
+        <is>
+          <t>ok_filtered_matrix_no_empty_droplet_background</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:K35"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Sample-level expression filtering after DecontX for GSE194078 and GSE286068; distinct from doublet-union singlet retention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Source: results/qc/GSE194078_postdecont_qc_summary.csv; results/qc/GSE286068_postdecont_qc_summary.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>sample_accession</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>n_postdoublet_input</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>n_postdecont_qc_pass</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>n_postdecont_removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827375</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>2461</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>2461</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827376</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>7480</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>7477</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827377</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>1765</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>1762</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827378</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>7629</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>7543</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827379</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>3546</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>3546</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827380</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>8497</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>8465</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827381</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>9467</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>9466</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827382</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>12965</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>12881</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827383</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>9029</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>9029</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827384</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>7187</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>7116</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827385</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>9009</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>9003</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827386</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>8654</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>8466</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827387</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>367</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>367</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827388</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>7717</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>7703</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827389</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>1748</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>1737</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827390</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>9897</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>9892</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827391</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>1813</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>1812</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827392</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>6576</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>6477</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827393</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>311</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>309</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827394</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>8826</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>8752</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827395</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>2264</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>2229</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827396</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>10695</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>10615</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>GSM8717331</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>2676</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>2629</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>GSM8717332</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>206</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>206</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>GSM8717333</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>587</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>587</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>GSM8717334</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>1350</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>GSM8717335</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>3195</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>3195</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>GSM8717336</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>2910</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>2908</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>GSM8717337</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="n">
+        <v>1148</v>
+      </c>
+      <c r="D33" s="17" t="n">
+        <v>1148</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>GSM8717338</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>324</v>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>324</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>GSM8717339</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="n">
+        <v>885</v>
+      </c>
+      <c r="D35" s="17" t="n">
+        <v>885</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>GSM8717340</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>712</v>
+      </c>
+      <c r="D36" s="17" t="n">
+        <v>711</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>GSM8717341</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>3504</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>3504</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>GSM8717342</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>GSM8717343</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>1996</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>GSM8717344</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>203</v>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>201</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>GSM8717345</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="n">
+        <v>115</v>
+      </c>
+      <c r="D41" s="17" t="n">
+        <v>112</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:E41"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Cohort eligibility for paired roots, trajectory reconstruction, disease discovery and external projection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Source: metadata/cohort_analysis_roles.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>paired_PBMC_CSF_root_reference</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>independent_trajectory_reconstruction</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>disease_discovery</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>external_fixed_score_projection</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>disease_comparison</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>analysis_scope</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Paired blood-CSF trajectory and MS-control discovery comparison</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>docs/ANALYSIS_SCOPE.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Trajectory only; non-MS participants have other inflammatory demyelinating diseases</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>docs/ANALYSIS_SCOPE.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>CSF-root trajectory and MS-control discovery comparison</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>docs/ANALYSIS_SCOPE.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>GSE328265</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>External disease cohort; newly sequenced participants only after exclusion of ten previously published participants</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>docs/ANALYSIS_SCOPE.md</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:H8"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1094,10 +3697,10 @@
           <t>paired CSF-PBMC trajectory and disease discovery</t>
         </is>
       </c>
-      <c r="C5" s="15" t="b">
+      <c r="C5" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="D5" s="15" t="b">
+      <c r="D5" s="16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1112,10 +3715,10 @@
           <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
         </is>
       </c>
-      <c r="C6" s="15" t="b">
+      <c r="C6" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="D6" s="15" t="b">
+      <c r="D6" s="16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1130,10 +3733,10 @@
           <t>CSF trajectory and disease discovery</t>
         </is>
       </c>
-      <c r="C7" s="15" t="b">
+      <c r="C7" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="D7" s="15" t="b">
+      <c r="D7" s="16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1148,10 +3751,10 @@
           <t>external projection of newly sequenced GSE327243-GSE328264 subjects</t>
         </is>
       </c>
-      <c r="C8" s="15" t="b">
+      <c r="C8" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="D8" s="15" t="b">
+      <c r="D8" s="16" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1169,7 +3772,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1189,14 +3792,14 @@
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>Harmonized discovery-cohort sample metadata.</t>
+          <t>Sample metadata for the three trajectory cohorts; GSE194078 is excluded from disease comparisons.</t>
         </is>
       </c>
     </row>
@@ -1332,10 +3935,10 @@
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M5" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M5" s="16" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -1395,10 +3998,10 @@
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M6" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M6" s="16" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
@@ -1458,10 +4061,10 @@
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M7" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
@@ -1521,10 +4124,10 @@
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M8" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
@@ -1584,10 +4187,10 @@
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M9" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
@@ -1647,10 +4250,10 @@
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M10" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -1710,10 +4313,10 @@
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M11" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
@@ -1773,10 +4376,10 @@
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M12" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -1836,10 +4439,10 @@
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M13" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M13" s="16" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -1899,10 +4502,10 @@
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M14" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M14" s="16" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -1962,10 +4565,10 @@
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M15" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M15" s="16" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -2025,10 +4628,10 @@
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M16" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M16" s="16" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -2088,10 +4691,10 @@
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M17" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
@@ -2151,10 +4754,10 @@
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M18" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M18" s="16" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
@@ -2214,10 +4817,10 @@
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M19" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M19" s="16" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
@@ -2277,10 +4880,10 @@
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M20" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M20" s="16" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -2340,10 +4943,10 @@
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M21" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M21" s="16" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
@@ -2403,10 +5006,10 @@
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M22" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M22" s="16" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -2466,10 +5069,10 @@
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M23" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M23" s="16" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
@@ -2529,10 +5132,10 @@
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M24" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M24" s="16" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -2592,10 +5195,10 @@
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M25" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M25" s="16" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -2655,10 +5258,10 @@
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>discovery</t>
-        </is>
-      </c>
-      <c r="M26" s="15" t="n"/>
+          <t>paired CSF-PBMC trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M26" s="16" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
@@ -2718,10 +5321,10 @@
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M27" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M27" s="16" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
@@ -2781,10 +5384,10 @@
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M28" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M28" s="16" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
@@ -2844,10 +5447,10 @@
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M29" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M29" s="16" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
@@ -2907,10 +5510,10 @@
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M30" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M30" s="16" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -2970,10 +5573,10 @@
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M31" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M31" s="16" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
@@ -3033,10 +5636,10 @@
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M32" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M32" s="16" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -3096,10 +5699,10 @@
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M33" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M33" s="16" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
@@ -3159,10 +5762,10 @@
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M34" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M34" s="16" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
@@ -3222,10 +5825,10 @@
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M35" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M35" s="16" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -3285,10 +5888,10 @@
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M36" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M36" s="16" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -3348,10 +5951,10 @@
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M37" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M37" s="16" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
@@ -3411,10 +6014,10 @@
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M38" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M38" s="16" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -3474,10 +6077,10 @@
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M39" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M39" s="16" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
@@ -3537,10 +6140,10 @@
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M40" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M40" s="16" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -3600,10 +6203,10 @@
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M41" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M41" s="16" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
@@ -3663,10 +6266,10 @@
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M42" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M42" s="16" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
@@ -3726,10 +6329,10 @@
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M43" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M43" s="16" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
@@ -3789,10 +6392,10 @@
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M44" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M44" s="16" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
@@ -3852,10 +6455,10 @@
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M45" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M45" s="16" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
@@ -3915,10 +6518,10 @@
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M46" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M46" s="16" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
@@ -3978,10 +6581,10 @@
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M47" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M47" s="16" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
@@ -4041,10 +6644,10 @@
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M48" s="15" t="n"/>
+          <t>independent paired trajectory replication; inflammatory non-MS donors excluded from disease contrasts</t>
+        </is>
+      </c>
+      <c r="M48" s="16" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
@@ -4104,10 +6707,10 @@
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M49" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M49" s="16" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
@@ -4167,10 +6770,10 @@
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M50" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M50" s="16" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
@@ -4230,10 +6833,10 @@
       </c>
       <c r="L51" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M51" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M51" s="16" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
@@ -4293,10 +6896,10 @@
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M52" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M52" s="16" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
@@ -4356,10 +6959,10 @@
       </c>
       <c r="L53" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M53" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M53" s="16" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
@@ -4419,10 +7022,10 @@
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M54" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M54" s="16" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
@@ -4482,10 +7085,10 @@
       </c>
       <c r="L55" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M55" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M55" s="16" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
@@ -4545,10 +7148,10 @@
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M56" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M56" s="16" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
@@ -4608,10 +7211,10 @@
       </c>
       <c r="L57" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M57" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M57" s="16" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
@@ -4671,10 +7274,10 @@
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M58" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M58" s="16" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
@@ -4734,10 +7337,10 @@
       </c>
       <c r="L59" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M59" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M59" s="16" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
@@ -4797,10 +7400,10 @@
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M60" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M60" s="16" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="14" t="inlineStr">
@@ -4860,10 +7463,10 @@
       </c>
       <c r="L61" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M61" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M61" s="16" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
@@ -4923,10 +7526,10 @@
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M62" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M62" s="16" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="14" t="inlineStr">
@@ -4986,10 +7589,10 @@
       </c>
       <c r="L63" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M63" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M63" s="16" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
@@ -5049,10 +7652,10 @@
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M64" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M64" s="16" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="14" t="inlineStr">
@@ -5112,10 +7715,10 @@
       </c>
       <c r="L65" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M65" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M65" s="16" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
@@ -5175,10 +7778,10 @@
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M66" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M66" s="16" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="14" t="inlineStr">
@@ -5238,10 +7841,10 @@
       </c>
       <c r="L67" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M67" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M67" s="16" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
@@ -5301,10 +7904,10 @@
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M68" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M68" s="16" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="14" t="inlineStr">
@@ -5364,10 +7967,10 @@
       </c>
       <c r="L69" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M69" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M69" s="16" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
@@ -5427,10 +8030,10 @@
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M70" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M70" s="16" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="14" t="inlineStr">
@@ -5490,10 +8093,10 @@
       </c>
       <c r="L71" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M71" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M71" s="16" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
@@ -5553,10 +8156,10 @@
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M72" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M72" s="16" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="14" t="inlineStr">
@@ -5616,10 +8219,10 @@
       </c>
       <c r="L73" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M73" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M73" s="16" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
@@ -5679,10 +8282,10 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>external_validation</t>
-        </is>
-      </c>
-      <c r="M74" s="15" t="n"/>
+          <t>CSF trajectory and disease discovery</t>
+        </is>
+      </c>
+      <c r="M74" s="16" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:M74"/>
@@ -5698,7 +8301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5806,7 +8409,7 @@
           <t>Ctrl_1</t>
         </is>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="14" t="inlineStr">
@@ -5856,7 +8459,7 @@
           <t>Ctrl_3</t>
         </is>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -5906,7 +8509,7 @@
           <t>Ctrl_4</t>
         </is>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="14" t="inlineStr">
@@ -5956,7 +8559,7 @@
           <t>Ctrl_5</t>
         </is>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -6006,7 +8609,7 @@
           <t>Ctrl_6</t>
         </is>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -6056,7 +8659,7 @@
           <t>Ctrl_7</t>
         </is>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -6106,7 +8709,7 @@
           <t>Ctrl_9</t>
         </is>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="14" t="inlineStr">
@@ -6156,7 +8759,7 @@
           <t>Ctrl_10</t>
         </is>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -6206,7 +8809,7 @@
           <t>PPMS_1</t>
         </is>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="14" t="inlineStr">
@@ -6256,7 +8859,7 @@
           <t>PPMS_2</t>
         </is>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -6306,7 +8909,7 @@
           <t>PPMS_3</t>
         </is>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="14" t="inlineStr">
@@ -6356,7 +8959,7 @@
           <t>PPMS_4</t>
         </is>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -6406,7 +9009,7 @@
           <t>PPMS_5</t>
         </is>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="14" t="inlineStr">
@@ -6456,7 +9059,7 @@
           <t>RRMS_1</t>
         </is>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -6506,7 +9109,7 @@
           <t>RRMS_2</t>
         </is>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -6556,7 +9159,7 @@
           <t>RRMS_3</t>
         </is>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -6606,7 +9209,7 @@
           <t>RRMS_4</t>
         </is>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="14" t="inlineStr">
@@ -6656,7 +9259,7 @@
           <t>RRMS_5</t>
         </is>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -6706,7 +9309,7 @@
           <t>RRMS_6</t>
         </is>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="14" t="inlineStr">
@@ -6756,7 +9359,7 @@
           <t>RRMS_7</t>
         </is>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -6806,7 +9409,7 @@
           <t>RRMS_8</t>
         </is>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="14" t="inlineStr">
@@ -6856,7 +9459,7 @@
           <t>RRMS_9</t>
         </is>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -6906,7 +9509,7 @@
           <t>SPMS_1</t>
         </is>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="14" t="inlineStr">
@@ -6956,7 +9559,7 @@
           <t>SPMS_2</t>
         </is>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -7006,7 +9609,7 @@
           <t>SPMS_3</t>
         </is>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="14" t="inlineStr">
@@ -7056,7 +9659,7 @@
           <t>PPMS_6</t>
         </is>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -7106,7 +9709,7 @@
           <t>SPMS_4</t>
         </is>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="E31" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="14" t="inlineStr">
@@ -7156,7 +9759,7 @@
           <t>SPMS_4</t>
         </is>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -7206,7 +9809,7 @@
           <t>SPMS_5</t>
         </is>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
@@ -7256,7 +9859,7 @@
           <t>SPMS_6</t>
         </is>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="E34" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -7306,7 +9909,7 @@
           <t>SPMS_7</t>
         </is>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="E35" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="14" t="inlineStr">
@@ -7349,7 +9952,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7427,7 +10030,7 @@
           <t>idiopathic intracranial hypertension</t>
         </is>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7452,7 +10055,7 @@
           <t>Multiple Sclerosis</t>
         </is>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7477,7 +10080,7 @@
           <t>idiopathic intracranial hypertension</t>
         </is>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>5</v>
       </c>
     </row>
@@ -7502,7 +10105,7 @@
           <t>Multiple Sclerosis</t>
         </is>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>5</v>
       </c>
     </row>
@@ -7527,7 +10130,7 @@
           <t>MS</t>
         </is>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7552,7 +10155,7 @@
           <t>Ab-mediated IDD</t>
         </is>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7577,7 +10180,7 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7602,7 +10205,7 @@
           <t>MS</t>
         </is>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7627,7 +10230,7 @@
           <t>Ab-mediated IDD</t>
         </is>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7652,7 +10255,7 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7677,7 +10280,7 @@
           <t>Multiple sclerosis</t>
         </is>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -7702,7 +10305,7 @@
           <t>PPMS</t>
         </is>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>5</v>
       </c>
     </row>
@@ -7727,7 +10330,7 @@
           <t>RRMS</t>
         </is>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7752,7 +10355,7 @@
           <t>SPMS</t>
         </is>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7777,7 +10380,7 @@
           <t>Healthy donor</t>
         </is>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7802,7 +10405,7 @@
           <t>NIND</t>
         </is>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7827,7 +10430,7 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7836,827 +10439,6 @@
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>Sample-level final QC, DecontX and doublet-union summary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Source: results/qc/GSE138266_cleanup_sample_summary.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>sample_accession</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>n_pre_doublet_qc</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>n_scrublet_doublets</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>n_scDblFinder_doublets</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>n_doublet_union</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>n_singlets</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>pct_doublet_union</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>median_decontX_contamination</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>decontX_status</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104122</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="n">
-        <v>4097</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>211</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>271</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>384</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>3713</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>9.372711740297779</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>0.0031809858472626</v>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104123</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n">
-        <v>2425</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>79</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>92</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>144</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>2281</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>5.93814432989691</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>0.0071041702969549</v>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104124</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n">
-        <v>3004</v>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>80</v>
-      </c>
-      <c r="D7" s="16" t="n">
-        <v>129</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>182</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>2822</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>6.05858854860186</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>0.0059341609648815</v>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104125</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n">
-        <v>1404</v>
-      </c>
-      <c r="C8" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>73</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>1331</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>5.1994301994302</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>0.0053488127196622</v>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104126</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n">
-        <v>7498</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>469</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>847</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>1107</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>6391</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>14.76393704988</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>0.0040197424668841</v>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104127</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n">
-        <v>872</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>838</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>3.89908256880734</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>0.0062176000379566</v>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104128</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>1127</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>51</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>1062</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>5.76752440106477</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>0.0199971768403324</v>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104129</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>3493</v>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>207</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>3253</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>6.87088462639565</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>0.0124734481578297</v>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104130</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>702</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>24</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>39</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>55</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>647</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>7.83475783475783</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>0.0287734227414245</v>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104131</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>1077</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>33</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>38</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>1039</v>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>3.52831940575673</v>
-      </c>
-      <c r="H14" s="15" t="n">
-        <v>0.009659482927068501</v>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104132</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
-        <v>8127</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>592</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>778</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>1076</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>7051</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>13.2398178909807</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>0.0201550087770198</v>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104133</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n">
-        <v>1070</v>
-      </c>
-      <c r="C16" s="16" t="n">
-        <v>41</v>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>71</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>999</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>6.63551401869159</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>0.0122060685503956</v>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104134</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>6089</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>313</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>444</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>518</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>5571</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>8.507144030218431</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>0.0287622259196381</v>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104135</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n">
-        <v>3340</v>
-      </c>
-      <c r="C18" s="16" t="n">
-        <v>90</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>157</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>180</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>3160</v>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>5.38922155688623</v>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>0.009523896002872999</v>
-      </c>
-      <c r="I18" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104136</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n">
-        <v>5146</v>
-      </c>
-      <c r="C19" s="16" t="n">
-        <v>216</v>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>269</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>355</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>4791</v>
-      </c>
-      <c r="G19" s="15" t="n">
-        <v>6.89856198989506</v>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>0.0264315580997685</v>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104137</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>3226</v>
-      </c>
-      <c r="C20" s="16" t="n">
-        <v>103</v>
-      </c>
-      <c r="D20" s="16" t="n">
-        <v>141</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>169</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>3057</v>
-      </c>
-      <c r="G20" s="15" t="n">
-        <v>5.23868567885927</v>
-      </c>
-      <c r="H20" s="15" t="n">
-        <v>0.0206289953172852</v>
-      </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104138</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="n">
-        <v>7740</v>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>506</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>477</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>661</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>7079</v>
-      </c>
-      <c r="G21" s="15" t="n">
-        <v>8.54005167958656</v>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>0.0217599347005032</v>
-      </c>
-      <c r="I21" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104139</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n">
-        <v>3316</v>
-      </c>
-      <c r="C22" s="16" t="n">
-        <v>88</v>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>136</v>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>3180</v>
-      </c>
-      <c r="G22" s="15" t="n">
-        <v>4.10132689987937</v>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>0.0173268037522625</v>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104140</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="n">
-        <v>3895</v>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>131</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>150</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>212</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>3683</v>
-      </c>
-      <c r="G23" s="15" t="n">
-        <v>5.44287548138639</v>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>0.0108675163948241</v>
-      </c>
-      <c r="I23" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104141</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n">
-        <v>1733</v>
-      </c>
-      <c r="C24" s="16" t="n">
-        <v>33</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>69</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>1664</v>
-      </c>
-      <c r="G24" s="15" t="n">
-        <v>3.98153491055972</v>
-      </c>
-      <c r="H24" s="15" t="n">
-        <v>0.0165693584587804</v>
-      </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104142</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="n">
-        <v>5146</v>
-      </c>
-      <c r="C25" s="16" t="n">
-        <v>220</v>
-      </c>
-      <c r="D25" s="16" t="n">
-        <v>284</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>336</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>4810</v>
-      </c>
-      <c r="G25" s="15" t="n">
-        <v>6.52934317916829</v>
-      </c>
-      <c r="H25" s="15" t="n">
-        <v>0.0231344163241006</v>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>GSM4104143</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>1497</v>
-      </c>
-      <c r="C26" s="16" t="n">
-        <v>22</v>
-      </c>
-      <c r="D26" s="16" t="n">
-        <v>33</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>52</v>
-      </c>
-      <c r="F26" s="16" t="n">
-        <v>1445</v>
-      </c>
-      <c r="G26" s="15" t="n">
-        <v>3.47361389445558</v>
-      </c>
-      <c r="H26" s="15" t="n">
-        <v>0.0016061259585416</v>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:I26"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -8689,14 +10471,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>Sample-level final QC, DecontX and doublet-union summary.</t>
+          <t>Sample-level doublet-union singlet counts and DecontX estimates, before post-decontamination expression filtering.</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Source: results/qc/GSE194078_cleanup_sample_summary.csv</t>
+          <t>Source: results/qc/GSE138266_cleanup_sample_summary.csv</t>
         </is>
       </c>
     </row>
@@ -8750,29 +10532,29 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>GSM5827375</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="n">
-        <v>2613</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>55</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>138</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>152</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>2461</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>5.81706850363567</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>0.0199768230057826</v>
+          <t>GSM4104122</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>4097</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>211</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>271</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>384</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>3713</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>9.372711740297779</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>0.0031809858472626</v>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
@@ -8783,29 +10565,29 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>GSM5827376</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n">
-        <v>8316</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>554</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>653</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>836</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>7480</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>10.0529100529101</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>0.036450100838699</v>
+          <t>GSM4104123</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>2425</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>79</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>92</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>144</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>2281</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>5.93814432989691</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>0.0071041702969549</v>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
@@ -8816,29 +10598,29 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>GSM5827377</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n">
-        <v>1849</v>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="D7" s="16" t="n">
-        <v>62</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>84</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>1765</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>4.54299621416982</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>0.0149807564937984</v>
+          <t>GSM4104124</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>3004</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>129</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>182</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>2822</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>6.05858854860186</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>0.0059341609648815</v>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
@@ -8849,29 +10631,29 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>GSM5827378</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n">
-        <v>8553</v>
-      </c>
-      <c r="C8" s="16" t="n">
-        <v>586</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>584</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>924</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>7629</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>10.8032269379165</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>0.0227976972158275</v>
+          <t>GSM4104125</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>1404</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>73</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>1331</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>5.1994301994302</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>0.0053488127196622</v>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
@@ -8882,29 +10664,29 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>GSM5827379</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n">
-        <v>3768</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>114</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>138</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>222</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>3546</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>5.89171974522293</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>0.0073058604491799</v>
+          <t>GSM4104126</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>7498</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>469</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>847</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>1107</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>6391</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>14.76393704988</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>0.0040197424668841</v>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
@@ -8915,29 +10697,29 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>GSM5827380</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n">
-        <v>9577</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>734</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>830</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>1080</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>8497</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>11.2770178552783</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>0.0404142527423651</v>
+          <t>GSM4104127</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>872</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>838</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>3.89908256880734</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>0.0062176000379566</v>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
@@ -8948,29 +10730,29 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>GSM5827381</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>10976</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>964</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>960</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>1509</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>9467</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>13.7481778425656</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>0.0277793487198101</v>
+          <t>GSM4104128</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>1127</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>51</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>1062</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>5.76752440106477</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>0.0199971768403324</v>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
@@ -8981,29 +10763,29 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>GSM5827382</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>15159</v>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>1516</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>1680</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>2194</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>12965</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>14.4732502143941</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>0.0063341517237531</v>
+          <t>GSM4104129</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>3493</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>116</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>207</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>240</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>3253</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>6.87088462639565</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>0.0124734481578297</v>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
@@ -9014,29 +10796,29 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>GSM5827383</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>10368</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>860</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>810</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>1339</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>9029</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>12.914737654321</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>0.0058355539394927</v>
+          <t>GSM4104130</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>702</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>647</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>7.83475783475783</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>0.0287734227414245</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -9047,29 +10829,29 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>GSM5827384</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>7928</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>503</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>634</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>741</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>7187</v>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>9.34661957618567</v>
-      </c>
-      <c r="H14" s="15" t="n">
-        <v>0.0283630652581957</v>
+          <t>GSM4104131</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>1077</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>1039</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>3.52831940575673</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>0.009659482927068501</v>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
@@ -9080,29 +10862,29 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>GSM5827385</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
-        <v>10204</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>833</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>761</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>1195</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>9009</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>11.7110936887495</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>0.0189629724460398</v>
+          <t>GSM4104132</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>8127</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>592</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>778</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>1076</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>7051</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>13.2398178909807</v>
+      </c>
+      <c r="H15" s="16" t="n">
+        <v>0.0201550087770198</v>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -9113,29 +10895,29 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>GSM5827386</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n">
-        <v>9614</v>
-      </c>
-      <c r="C16" s="16" t="n">
-        <v>740</v>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>648</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>960</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>8654</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>9.98543790305804</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>0.0167181474385543</v>
+          <t>GSM4104133</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>1070</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>71</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>999</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>6.63551401869159</v>
+      </c>
+      <c r="H16" s="16" t="n">
+        <v>0.0122060685503956</v>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
@@ -9146,29 +10928,29 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>GSM5827387</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>385</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>16</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>367</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>4.67532467532468</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>0.0084410659567285</v>
+          <t>GSM4104134</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>6089</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>313</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>444</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>518</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>5571</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>8.507144030218431</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <v>0.0287622259196381</v>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
@@ -9179,29 +10961,29 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>GSM5827388</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n">
-        <v>8698</v>
-      </c>
-      <c r="C18" s="16" t="n">
-        <v>606</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>827</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>981</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>7717</v>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>11.2784548171994</v>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>0.039423203862577</v>
+          <t>GSM4104135</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>3340</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>157</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>180</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>3160</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>5.38922155688623</v>
+      </c>
+      <c r="H18" s="16" t="n">
+        <v>0.009523896002872999</v>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
@@ -9212,29 +10994,29 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>GSM5827389</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n">
-        <v>1823</v>
-      </c>
-      <c r="C19" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>52</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>75</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>1748</v>
-      </c>
-      <c r="G19" s="15" t="n">
-        <v>4.11409764125069</v>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>0.0075409796567404</v>
+          <t>GSM4104136</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>5146</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>216</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>269</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>355</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>4791</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>6.89856198989506</v>
+      </c>
+      <c r="H19" s="16" t="n">
+        <v>0.0264315580997685</v>
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
@@ -9245,29 +11027,29 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>GSM5827390</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>11247</v>
-      </c>
-      <c r="C20" s="16" t="n">
-        <v>1012</v>
-      </c>
-      <c r="D20" s="16" t="n">
-        <v>1106</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>1350</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>9897</v>
-      </c>
-      <c r="G20" s="15" t="n">
-        <v>12.003200853561</v>
-      </c>
-      <c r="H20" s="15" t="n">
-        <v>0.0214582399722554</v>
+          <t>GSM4104137</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>3226</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>103</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>141</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>169</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>3057</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>5.23868567885927</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>0.0206289953172852</v>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
@@ -9278,29 +11060,29 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>GSM5827391</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="n">
-        <v>1945</v>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>31</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>112</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>132</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>1813</v>
-      </c>
-      <c r="G21" s="15" t="n">
-        <v>6.7866323907455</v>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>0.0102091740700431</v>
+          <t>GSM4104138</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>7740</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>506</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>477</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>661</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>7079</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>8.54005167958656</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>0.0217599347005032</v>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
@@ -9311,29 +11093,29 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>GSM5827392</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n">
-        <v>7406</v>
-      </c>
-      <c r="C22" s="16" t="n">
-        <v>439</v>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>692</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>830</v>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>6576</v>
-      </c>
-      <c r="G22" s="15" t="n">
-        <v>11.2071293545774</v>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>0.038438054268339</v>
+          <t>GSM4104139</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>3316</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>88</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>136</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>3180</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <v>4.10132689987937</v>
+      </c>
+      <c r="H22" s="16" t="n">
+        <v>0.0173268037522625</v>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
@@ -9344,29 +11126,29 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>GSM5827393</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="n">
-        <v>327</v>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>16</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>311</v>
-      </c>
-      <c r="G23" s="15" t="n">
-        <v>4.89296636085627</v>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>0.0105819069859653</v>
+          <t>GSM4104140</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>3895</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>131</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>212</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>3683</v>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>5.44287548138639</v>
+      </c>
+      <c r="H23" s="16" t="n">
+        <v>0.0108675163948241</v>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
@@ -9377,29 +11159,29 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>GSM5827394</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n">
-        <v>9991</v>
-      </c>
-      <c r="C24" s="16" t="n">
-        <v>799</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>901</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>1165</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>8826</v>
-      </c>
-      <c r="G24" s="15" t="n">
-        <v>11.6604944450005</v>
-      </c>
-      <c r="H24" s="15" t="n">
-        <v>0.0813238121571767</v>
+          <t>GSM4104141</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>1733</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>69</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>1664</v>
+      </c>
+      <c r="G24" s="16" t="n">
+        <v>3.98153491055972</v>
+      </c>
+      <c r="H24" s="16" t="n">
+        <v>0.0165693584587804</v>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
@@ -9410,29 +11192,29 @@
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>GSM5827395</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="n">
-        <v>2381</v>
-      </c>
-      <c r="C25" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="D25" s="16" t="n">
-        <v>82</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>117</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>2264</v>
-      </c>
-      <c r="G25" s="15" t="n">
-        <v>4.91390172196556</v>
-      </c>
-      <c r="H25" s="15" t="n">
-        <v>0.0078645361372517</v>
+          <t>GSM4104142</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n">
+        <v>5146</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>220</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>284</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>336</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>4810</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <v>6.52934317916829</v>
+      </c>
+      <c r="H25" s="16" t="n">
+        <v>0.0231344163241006</v>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
@@ -9443,29 +11225,29 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>GSM5827396</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>12579</v>
-      </c>
-      <c r="C26" s="16" t="n">
-        <v>1258</v>
-      </c>
-      <c r="D26" s="16" t="n">
-        <v>1268</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>1884</v>
-      </c>
-      <c r="F26" s="16" t="n">
-        <v>10695</v>
-      </c>
-      <c r="G26" s="15" t="n">
-        <v>14.9773431910327</v>
-      </c>
-      <c r="H26" s="15" t="n">
-        <v>0.0437492655459446</v>
+          <t>GSM4104143</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>1497</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <v>1445</v>
+      </c>
+      <c r="G26" s="16" t="n">
+        <v>3.47361389445558</v>
+      </c>
+      <c r="H26" s="16" t="n">
+        <v>0.0016061259585416</v>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
@@ -9488,6 +11270,827 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Sample-level doublet-union singlet counts and DecontX estimates, before post-decontamination expression filtering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Source: results/qc/GSE194078_cleanup_sample_summary.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>sample_accession</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>n_pre_doublet_qc</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>n_scrublet_doublets</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>n_scDblFinder_doublets</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>n_doublet_union</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>n_singlets</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>pct_doublet_union</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>median_decontX_contamination</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>decontX_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827375</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>2613</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>138</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>152</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>2461</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>5.81706850363567</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>0.0199768230057826</v>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827376</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>8316</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>554</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>653</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>836</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>7480</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>10.0529100529101</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>0.036450100838699</v>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827377</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>1849</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>1765</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>4.54299621416982</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>0.0149807564937984</v>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827378</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>8553</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>586</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>584</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>924</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>7629</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>10.8032269379165</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>0.0227976972158275</v>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827379</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>3768</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>114</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>138</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>222</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>3546</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>5.89171974522293</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>0.0073058604491799</v>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827380</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>9577</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>734</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>830</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>8497</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>11.2770178552783</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>0.0404142527423651</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827381</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>10976</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>964</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>960</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>1509</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>9467</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>13.7481778425656</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>0.0277793487198101</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827382</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>15159</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>1516</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>1680</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>2194</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>12965</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>14.4732502143941</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>0.0063341517237531</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827383</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>10368</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>860</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>810</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>9029</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>12.914737654321</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>0.0058355539394927</v>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827384</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>7928</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>503</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>634</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>741</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>7187</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>9.34661957618567</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>0.0283630652581957</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827385</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>10204</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>833</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>761</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>1195</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>9009</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>11.7110936887495</v>
+      </c>
+      <c r="H15" s="16" t="n">
+        <v>0.0189629724460398</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827386</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>9614</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>740</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>648</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>960</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>8654</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>9.98543790305804</v>
+      </c>
+      <c r="H16" s="16" t="n">
+        <v>0.0167181474385543</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827387</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>385</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>367</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>4.67532467532468</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <v>0.0084410659567285</v>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827388</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>8698</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>606</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>827</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>981</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>7717</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>11.2784548171994</v>
+      </c>
+      <c r="H18" s="16" t="n">
+        <v>0.039423203862577</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827389</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>1823</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>1748</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>4.11409764125069</v>
+      </c>
+      <c r="H19" s="16" t="n">
+        <v>0.0075409796567404</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827390</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>11247</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>1012</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>1106</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>9897</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>12.003200853561</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>0.0214582399722554</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827391</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>1945</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>112</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>132</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>1813</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>6.7866323907455</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>0.0102091740700431</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827392</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>7406</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>439</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>692</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>830</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>6576</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <v>11.2071293545774</v>
+      </c>
+      <c r="H22" s="16" t="n">
+        <v>0.038438054268339</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827393</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>327</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>311</v>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>4.89296636085627</v>
+      </c>
+      <c r="H23" s="16" t="n">
+        <v>0.0105819069859653</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827394</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>9991</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>799</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>901</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>1165</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>8826</v>
+      </c>
+      <c r="G24" s="16" t="n">
+        <v>11.6604944450005</v>
+      </c>
+      <c r="H24" s="16" t="n">
+        <v>0.0813238121571767</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827395</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n">
+        <v>2381</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>82</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>2264</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <v>4.91390172196556</v>
+      </c>
+      <c r="H25" s="16" t="n">
+        <v>0.0078645361372517</v>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>GSM5827396</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>12579</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>1258</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>1268</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>1884</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <v>10695</v>
+      </c>
+      <c r="G26" s="16" t="n">
+        <v>14.9773431910327</v>
+      </c>
+      <c r="H26" s="16" t="n">
+        <v>0.0437492655459446</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:I26"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9510,7 +12113,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>Sample-level final QC, DecontX and doublet-union summary.</t>
+          <t>Sample-level doublet-union singlet counts and DecontX estimates, before post-decontamination expression filtering.</t>
         </is>
       </c>
     </row>
@@ -9574,25 +12177,25 @@
           <t>GSM8717331</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>2908</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>68</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>192</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>232</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>2676</v>
       </c>
-      <c r="G5" s="15" t="n">
+      <c r="G5" s="16" t="n">
         <v>7.97799174690509</v>
       </c>
-      <c r="H5" s="15" t="n">
+      <c r="H5" s="16" t="n">
         <v>0.0129202840970095</v>
       </c>
       <c r="I5" s="14" t="inlineStr">
@@ -9607,25 +12210,25 @@
           <t>GSM8717332</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>214</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>206</v>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="G6" s="16" t="n">
         <v>3.73831775700935</v>
       </c>
-      <c r="H6" s="15" t="n">
+      <c r="H6" s="16" t="n">
         <v>0.009033315268619699</v>
       </c>
       <c r="I6" s="14" t="inlineStr">
@@ -9640,25 +12243,25 @@
           <t>GSM8717333</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>611</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>21</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>587</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="16" t="n">
         <v>3.92798690671031</v>
       </c>
-      <c r="H7" s="15" t="n">
+      <c r="H7" s="16" t="n">
         <v>0.015153982695145</v>
       </c>
       <c r="I7" s="14" t="inlineStr">
@@ -9673,25 +12276,25 @@
           <t>GSM8717334</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>1420</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>55</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>70</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>1350</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="16" t="n">
         <v>4.92957746478873</v>
       </c>
-      <c r="H8" s="15" t="n">
+      <c r="H8" s="16" t="n">
         <v>0.0506819199420937</v>
       </c>
       <c r="I8" s="14" t="inlineStr">
@@ -9706,25 +12309,25 @@
           <t>GSM8717335</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>3453</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>96</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>190</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>258</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>3195</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="16" t="n">
         <v>7.47176368375326</v>
       </c>
-      <c r="H9" s="15" t="n">
+      <c r="H9" s="16" t="n">
         <v>0.0128467088693348</v>
       </c>
       <c r="I9" s="14" t="inlineStr">
@@ -9739,25 +12342,25 @@
           <t>GSM8717336</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>3155</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>80</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>204</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>245</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>2910</v>
       </c>
-      <c r="G10" s="15" t="n">
+      <c r="G10" s="16" t="n">
         <v>7.76545166402536</v>
       </c>
-      <c r="H10" s="15" t="n">
+      <c r="H10" s="16" t="n">
         <v>0.0306132970065866</v>
       </c>
       <c r="I10" s="14" t="inlineStr">
@@ -9772,25 +12375,25 @@
           <t>GSM8717337</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>1197</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>38</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>49</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>1148</v>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="16" t="n">
         <v>4.09356725146199</v>
       </c>
-      <c r="H11" s="15" t="n">
+      <c r="H11" s="16" t="n">
         <v>0.0423664056286287</v>
       </c>
       <c r="I11" s="14" t="inlineStr">
@@ -9805,25 +12408,25 @@
           <t>GSM8717338</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>334</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>324</v>
       </c>
-      <c r="G12" s="15" t="n">
+      <c r="G12" s="16" t="n">
         <v>2.9940119760479</v>
       </c>
-      <c r="H12" s="15" t="n">
+      <c r="H12" s="16" t="n">
         <v>0.0324586567983363</v>
       </c>
       <c r="I12" s="14" t="inlineStr">
@@ -9838,25 +12441,25 @@
           <t>GSM8717339</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>908</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>885</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="16" t="n">
         <v>2.53303964757709</v>
       </c>
-      <c r="H13" s="15" t="n">
+      <c r="H13" s="16" t="n">
         <v>0.0393833559063165</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
@@ -9871,25 +12474,25 @@
           <t>GSM8717340</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>742</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>26</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>712</v>
       </c>
-      <c r="G14" s="15" t="n">
+      <c r="G14" s="16" t="n">
         <v>4.04312668463612</v>
       </c>
-      <c r="H14" s="15" t="n">
+      <c r="H14" s="16" t="n">
         <v>0.0026306557694056</v>
       </c>
       <c r="I14" s="14" t="inlineStr">
@@ -9904,25 +12507,25 @@
           <t>GSM8717341</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>3775</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>115</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>203</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>271</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>3504</v>
       </c>
-      <c r="G15" s="15" t="n">
+      <c r="G15" s="16" t="n">
         <v>7.17880794701987</v>
       </c>
-      <c r="H15" s="15" t="n">
+      <c r="H15" s="16" t="n">
         <v>0.0120025067473005</v>
       </c>
       <c r="I15" s="14" t="inlineStr">
@@ -9937,25 +12540,25 @@
           <t>GSM8717342</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>3239</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>84</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>175</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>233</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>3006</v>
       </c>
-      <c r="G16" s="15" t="n">
+      <c r="G16" s="16" t="n">
         <v>7.19357826489657</v>
       </c>
-      <c r="H16" s="15" t="n">
+      <c r="H16" s="16" t="n">
         <v>0.0370696871132611</v>
       </c>
       <c r="I16" s="14" t="inlineStr">
@@ -9970,25 +12573,25 @@
           <t>GSM8717343</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>2104</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>36</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>69</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <v>2004</v>
       </c>
-      <c r="G17" s="15" t="n">
+      <c r="G17" s="16" t="n">
         <v>4.75285171102662</v>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="H17" s="16" t="n">
         <v>0.08971424716171041</v>
       </c>
       <c r="I17" s="14" t="inlineStr">
@@ -10003,25 +12606,25 @@
           <t>GSM8717344</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>218</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>203</v>
       </c>
-      <c r="G18" s="15" t="n">
+      <c r="G18" s="16" t="n">
         <v>6.88073394495413</v>
       </c>
-      <c r="H18" s="15" t="n">
+      <c r="H18" s="16" t="n">
         <v>0.140732127130717</v>
       </c>
       <c r="I18" s="14" t="inlineStr">
@@ -10036,25 +12639,25 @@
           <t>GSM8717345</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>124</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <v>115</v>
       </c>
-      <c r="G19" s="15" t="n">
+      <c r="G19" s="16" t="n">
         <v>7.25806451612903</v>
       </c>
-      <c r="H19" s="15" t="n">
+      <c r="H19" s="16" t="n">
         <v>0.0013065133497969</v>
       </c>
       <c r="I19" s="14" t="inlineStr">
@@ -10075,1442 +12678,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:K35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="42" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>Sample-level final QC, DecontX and doublet-union summary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Source: results/qc/GSE328265_cleanup_sample_summary.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>sample_accession</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>subject_id</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>diagnosis</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>n_qc_pass</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>n_scrublet_doublets</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>n_scDblFinder_doublets</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>n_doublet_union</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>n_singlets</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>pct_doublet_union</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>median_decontX_contamination</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>decontX_status</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>GSM9651991</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Ctrl_1</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>Ctrl</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>949</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>42</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>907</v>
-      </c>
-      <c r="I5" s="15" t="n">
-        <v>4.42571127502634</v>
-      </c>
-      <c r="J5" s="15" t="n">
-        <v>0.0069212043861581</v>
-      </c>
-      <c r="K5" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>GSM9651992</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>Ctrl_3</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>Ctrl</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>506</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>485</v>
-      </c>
-      <c r="I6" s="15" t="n">
-        <v>4.1501976284585</v>
-      </c>
-      <c r="J6" s="15" t="n">
-        <v>0.0103990633106001</v>
-      </c>
-      <c r="K6" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>GSM9651993</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Ctrl_4</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Ctrl</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="n">
-        <v>847</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>820</v>
-      </c>
-      <c r="I7" s="15" t="n">
-        <v>3.18772136953955</v>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>0.0065734772454175</v>
-      </c>
-      <c r="K7" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>GSM9651994</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>Ctrl_5</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Ctrl</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>2515</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>51</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>147</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>174</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>2341</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>6.91848906560636</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>0.0117902681770771</v>
-      </c>
-      <c r="K8" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>GSM9651995</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Ctrl_6</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Ctrl</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>364</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="H9" s="16" t="n">
-        <v>356</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>2.1978021978022</v>
-      </c>
-      <c r="J9" s="15" t="n">
-        <v>0.008211764616374399</v>
-      </c>
-      <c r="K9" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>GSM9651996</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Ctrl_7</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Ctrl</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="15" t="n"/>
-      <c r="K10" s="14" t="inlineStr">
-        <is>
-          <t>not_run_lt_50_singlets</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>GSM9651997</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>Ctrl_9</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Ctrl</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>479</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>460</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>3.96659707724426</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>0.101773605686458</v>
-      </c>
-      <c r="K11" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>GSM9651998</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Ctrl_10</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Ctrl</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>2199</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>39</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>95</v>
-      </c>
-      <c r="H12" s="16" t="n">
-        <v>2104</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>4.32014552069122</v>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>0.026205776626616</v>
-      </c>
-      <c r="K12" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>GSM9651999</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>PPMS_1</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>PPMS</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>313</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="H13" s="16" t="n">
-        <v>302</v>
-      </c>
-      <c r="I13" s="15" t="n">
-        <v>3.51437699680511</v>
-      </c>
-      <c r="J13" s="15" t="n">
-        <v>0.009097831093387999</v>
-      </c>
-      <c r="K13" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>GSM9652000</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>PPMS_2</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>PPMS</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>484</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="H14" s="16" t="n">
-        <v>470</v>
-      </c>
-      <c r="I14" s="15" t="n">
-        <v>2.89256198347107</v>
-      </c>
-      <c r="J14" s="15" t="n">
-        <v>0.008623103775787301</v>
-      </c>
-      <c r="K14" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>GSM9652001</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>PPMS_3</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>PPMS</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>244</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="H15" s="16" t="n">
-        <v>235</v>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>3.68852459016393</v>
-      </c>
-      <c r="J15" s="15" t="n">
-        <v>0.0050243298464545</v>
-      </c>
-      <c r="K15" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>GSM9652002</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>PPMS_4</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>PPMS</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>243</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="G16" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="H16" s="16" t="n">
-        <v>232</v>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v>4.52674897119342</v>
-      </c>
-      <c r="J16" s="15" t="n">
-        <v>0.0191733597514777</v>
-      </c>
-      <c r="K16" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>GSM9652003</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>PPMS_5</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>PPMS</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>80</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="H17" s="16" t="n">
-        <v>69</v>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="J17" s="15" t="n">
-        <v>0.0337171534663794</v>
-      </c>
-      <c r="K17" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>GSM9652004</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>RRMS_1</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>RRMS</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>527</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="G18" s="16" t="n">
-        <v>22</v>
-      </c>
-      <c r="H18" s="16" t="n">
-        <v>505</v>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v>4.17457305502846</v>
-      </c>
-      <c r="J18" s="15" t="n">
-        <v>0.008260764005817101</v>
-      </c>
-      <c r="K18" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>GSM9652005</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>RRMS_2</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>RRMS</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>4498</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>162</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>302</v>
-      </c>
-      <c r="G19" s="16" t="n">
-        <v>381</v>
-      </c>
-      <c r="H19" s="16" t="n">
-        <v>4117</v>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v>8.47043130280125</v>
-      </c>
-      <c r="J19" s="15" t="n">
-        <v>0.0006277716992767</v>
-      </c>
-      <c r="K19" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>GSM9652006</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>RRMS_3</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>RRMS</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="n">
-        <v>10057</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>810</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>1199</v>
-      </c>
-      <c r="G20" s="16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="H20" s="16" t="n">
-        <v>8457</v>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v>15.9093168937059</v>
-      </c>
-      <c r="J20" s="15" t="n">
-        <v>0.0003035803005858</v>
-      </c>
-      <c r="K20" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>GSM9652007</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>RRMS_4</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>RRMS</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>1307</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>36</v>
-      </c>
-      <c r="G21" s="16" t="n">
-        <v>47</v>
-      </c>
-      <c r="H21" s="16" t="n">
-        <v>1260</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>3.59602142310635</v>
-      </c>
-      <c r="J21" s="15" t="n">
-        <v>0.0056808729767499</v>
-      </c>
-      <c r="K21" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>GSM9652008</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>RRMS_5</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>RRMS</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>400</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="G22" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="H22" s="16" t="n">
-        <v>385</v>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J22" s="15" t="n">
-        <v>0.0114590565810807</v>
-      </c>
-      <c r="K22" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>GSM9652009</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>RRMS_6</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>RRMS</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>2733</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>145</v>
-      </c>
-      <c r="G23" s="16" t="n">
-        <v>184</v>
-      </c>
-      <c r="H23" s="16" t="n">
-        <v>2549</v>
-      </c>
-      <c r="I23" s="15" t="n">
-        <v>6.73252835711672</v>
-      </c>
-      <c r="J23" s="15" t="n">
-        <v>0.0085876594704894</v>
-      </c>
-      <c r="K23" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>GSM9652010</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>RRMS_7</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>RRMS</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>2793</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>63</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>154</v>
-      </c>
-      <c r="G24" s="16" t="n">
-        <v>191</v>
-      </c>
-      <c r="H24" s="16" t="n">
-        <v>2602</v>
-      </c>
-      <c r="I24" s="15" t="n">
-        <v>6.83852488363767</v>
-      </c>
-      <c r="J24" s="15" t="n">
-        <v>0.0007245457728044</v>
-      </c>
-      <c r="K24" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>GSM9652011</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>RRMS_8</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>RRMS</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="n">
-        <v>66</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="H25" s="16" t="n">
-        <v>61</v>
-      </c>
-      <c r="I25" s="15" t="n">
-        <v>7.57575757575758</v>
-      </c>
-      <c r="J25" s="15" t="n">
-        <v>0.07025013731803489</v>
-      </c>
-      <c r="K25" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>GSM9652012</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>RRMS_9</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>RRMS</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="n">
-        <v>712</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="F26" s="16" t="n">
-        <v>31</v>
-      </c>
-      <c r="G26" s="16" t="n">
-        <v>39</v>
-      </c>
-      <c r="H26" s="16" t="n">
-        <v>673</v>
-      </c>
-      <c r="I26" s="15" t="n">
-        <v>5.47752808988764</v>
-      </c>
-      <c r="J26" s="15" t="n">
-        <v>0.0150314566845329</v>
-      </c>
-      <c r="K26" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>GSM9652013</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>SPMS_1</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>SPMS</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>390</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="G27" s="16" t="n">
-        <v>16</v>
-      </c>
-      <c r="H27" s="16" t="n">
-        <v>374</v>
-      </c>
-      <c r="I27" s="15" t="n">
-        <v>4.1025641025641</v>
-      </c>
-      <c r="J27" s="15" t="n">
-        <v>0.0111916952800713</v>
-      </c>
-      <c r="K27" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>GSM9652014</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>SPMS_2</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>SPMS</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="n">
-        <v>2013</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>33</v>
-      </c>
-      <c r="F28" s="16" t="n">
-        <v>101</v>
-      </c>
-      <c r="G28" s="16" t="n">
-        <v>120</v>
-      </c>
-      <c r="H28" s="16" t="n">
-        <v>1893</v>
-      </c>
-      <c r="I28" s="15" t="n">
-        <v>5.96125186289121</v>
-      </c>
-      <c r="J28" s="15" t="n">
-        <v>0.009328309626757099</v>
-      </c>
-      <c r="K28" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>GSM9652015</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>SPMS_3</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>SPMS</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>732</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="G29" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="H29" s="16" t="n">
-        <v>703</v>
-      </c>
-      <c r="I29" s="15" t="n">
-        <v>3.96174863387978</v>
-      </c>
-      <c r="J29" s="15" t="n">
-        <v>0.0132433108291693</v>
-      </c>
-      <c r="K29" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>GSM9677400</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>PPMS_6</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>PPMS</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="n">
-        <v>11808</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>1116</v>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>1296</v>
-      </c>
-      <c r="G30" s="16" t="n">
-        <v>1809</v>
-      </c>
-      <c r="H30" s="16" t="n">
-        <v>9999</v>
-      </c>
-      <c r="I30" s="15" t="n">
-        <v>15.3201219512195</v>
-      </c>
-      <c r="J30" s="15" t="n">
-        <v>0.0352331029380918</v>
-      </c>
-      <c r="K30" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>GSM9677401</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>SPMS_4</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>SPMS</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>843</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="G31" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="H31" s="16" t="n">
-        <v>809</v>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v>4.03321470937129</v>
-      </c>
-      <c r="J31" s="15" t="n">
-        <v>0.0002173787985738</v>
-      </c>
-      <c r="K31" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>GSM9677402</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>SPMS_4</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>SPMS</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="n">
-        <v>4371</v>
-      </c>
-      <c r="E32" s="16" t="n">
-        <v>153</v>
-      </c>
-      <c r="F32" s="16" t="n">
-        <v>264</v>
-      </c>
-      <c r="G32" s="16" t="n">
-        <v>353</v>
-      </c>
-      <c r="H32" s="16" t="n">
-        <v>4018</v>
-      </c>
-      <c r="I32" s="15" t="n">
-        <v>8.07595515900252</v>
-      </c>
-      <c r="J32" s="15" t="n">
-        <v>0.0012079561137204</v>
-      </c>
-      <c r="K32" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>GSM9677403</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>SPMS_5</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="inlineStr">
-        <is>
-          <t>SPMS</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="n">
-        <v>234</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F33" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="G33" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="H33" s="16" t="n">
-        <v>221</v>
-      </c>
-      <c r="I33" s="15" t="n">
-        <v>5.55555555555556</v>
-      </c>
-      <c r="J33" s="15" t="n">
-        <v>0.0081235072473752</v>
-      </c>
-      <c r="K33" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>GSM9677404</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>SPMS_6</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="inlineStr">
-        <is>
-          <t>SPMS</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="n">
-        <v>631</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="F34" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="G34" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="H34" s="16" t="n">
-        <v>611</v>
-      </c>
-      <c r="I34" s="15" t="n">
-        <v>3.16957210776545</v>
-      </c>
-      <c r="J34" s="15" t="n">
-        <v>0.0058398404081722</v>
-      </c>
-      <c r="K34" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>GSM9677405</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>SPMS_7</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>SPMS</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>1748</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="F35" s="16" t="n">
-        <v>79</v>
-      </c>
-      <c r="G35" s="16" t="n">
-        <v>84</v>
-      </c>
-      <c r="H35" s="16" t="n">
-        <v>1664</v>
-      </c>
-      <c r="I35" s="15" t="n">
-        <v>4.80549199084668</v>
-      </c>
-      <c r="J35" s="15" t="n">
-        <v>0.032806177331442</v>
-      </c>
-      <c r="K35" s="14" t="inlineStr">
-        <is>
-          <t>ok_filtered_matrix_no_empty_droplet_background</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:K35"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>